--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="397">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -716,7 +716,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -759,11 +762,11 @@
     <t>PractitionerRole.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value | Namespace du RASS (inconnu à ce jour)</t>
+    <t>The namespace for the identifier value | Namespace du RASS)</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.
-Namespace du RASS (inconnu à ce jour)</t>
+Namespace du RASS)</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -975,7 +978,7 @@
     <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation</t>
   </si>
   <si>
-    <t>The role a person plays representing an organization | Situation d'exercice (Fonction dans le NOS)</t>
+    <t>Roles which this practitioner is authorized to perform for the organization.</t>
   </si>
   <si>
     <t>A person may have more than one role.</t>
@@ -984,9 +987,6 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation. Correspond à la notion de Fonction dans le NOS.</t>
-  </si>
-  <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
@@ -999,7 +999,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation</t>
+    <t>Specific specialty associated with the organization | spécialité ordinale du professionnel de santé au sein de l'organisation</t>
   </si>
   <si>
     <t>Specific specialty of the practitioner.</t>
@@ -1144,7 +1144,10 @@
     <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/days-of-week</t>
+    <t>The days of the week.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/days-of-week|4.0.1</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime.allDay</t>
@@ -1584,7 +1587,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="168.7265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.15625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -4294,9 +4297,11 @@
       <c r="X24" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4314,7 +4319,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4332,7 +4337,7 @@
         <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4343,10 +4348,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4369,19 +4374,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4409,10 +4414,10 @@
         <v>152</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4430,7 +4435,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4445,10 +4450,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4459,10 +4464,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4488,16 +4493,16 @@
         <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4510,7 +4515,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4546,7 +4551,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4561,13 +4566,13 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4575,10 +4580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4604,13 +4609,13 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4624,7 +4629,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4660,7 +4665,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4675,13 +4680,13 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4689,10 +4694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4715,16 +4720,16 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4774,7 +4779,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4786,16 +4791,16 @@
         <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4803,10 +4808,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4829,16 +4834,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4888,7 +4893,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4900,16 +4905,16 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4917,10 +4922,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4943,70 +4948,70 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="R30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="P30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="R30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5021,24 +5026,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5061,19 +5066,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5122,7 +5127,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5134,27 +5139,27 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5177,16 +5182,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5236,7 +5241,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5248,13 +5253,13 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5265,10 +5270,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5291,16 +5296,16 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5350,7 +5355,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5362,13 +5367,13 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5379,10 +5384,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5405,19 +5410,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5442,11 +5447,9 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
         <v>312</v>
       </c>
@@ -5466,7 +5469,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5487,7 +5490,7 @@
         <v>314</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5521,7 +5524,7 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>316</v>
@@ -5642,7 +5645,7 @@
         <v>326</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5704,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5756,7 +5759,7 @@
         <v>333</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5818,7 +5821,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>334</v>
@@ -6468,9 +6471,11 @@
       <c r="X43" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y43" s="2"/>
+      <c r="Y43" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6517,10 +6522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6543,13 +6548,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6600,7 +6605,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6629,10 +6634,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6655,16 +6660,16 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6714,7 +6719,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6743,10 +6748,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6769,16 +6774,16 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6828,7 +6833,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6857,10 +6862,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6886,10 +6891,10 @@
         <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6940,7 +6945,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6969,10 +6974,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7081,10 +7086,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7195,10 +7200,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7311,10 +7316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7340,10 +7345,10 @@
         <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>361</v>
@@ -7396,7 +7401,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7425,10 +7430,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7451,16 +7456,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7510,7 +7515,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7522,10 +7527,10 @@
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>350</v>
@@ -7539,10 +7544,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7568,10 +7573,10 @@
         <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>361</v>
@@ -7624,7 +7629,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7653,10 +7658,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7679,19 +7684,19 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7740,7 +7745,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7752,13 +7757,13 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/main/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
